--- a/stories/arbres/ATOM-TMP.SAI.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Florent marche vers l'école. Maman tient sa main. Papa a mis le manteau dans le sac. Ils passent sous un grand arbre. Maman dit : il y a quatre saisons. Au printemps, Florent voit des fleurs. En été, il fait chaud. Florent boit de l'eau. En automne, les feuilles tombent. Elles sont jaunes. En hiver, Florent met son manteau. Maman dit un signe chacune. Fleurs, chaud, feuilles, manteau. Florent répète : quatre saisons. Papa arrive au portail. Il dit : quatre saisons.</t>
+          <t>Florent marche vers l'école. Maman tient sa main. Papa a mis le manteau dans le sac. Ils passent sous un grand arbre. Il y a quatre saisons. Au printemps, Florent voit des fleurs. En été, il fait chaud. Florent boit de l'eau. En automne, les feuilles tombent. Elles sont jaunes. En hiver, Florent met son manteau. Maman dit un signe chacune. Fleurs, chaud, feuilles, manteau. Florent répète : quatre saisons. Papa arrive au portail. Quatre saisons.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Florent marche vers l'école. Maman tient sa main. Papa a mis le manteau dans le sac. Ils passent sous un grand arbre.
+maman|Il y a quatre saisons. Au printemps, Florent voit des fleurs. En été, il fait chaud.
+narrateur|Florent boit de l'eau. En automne, les feuilles tombent. Elles sont jaunes. En hiver, Florent met son manteau. Maman dit un signe chacune. Fleurs, chaud, feuilles, manteau. Florent répète : quatre saisons. Papa arrive au portail.
+narrateur|Quatre saisons.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Il fait chaud. Quelle saison est-ce ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Florent a nommé les quatre saisons. Un signe chacune. Maman l'a aidé.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Florent ramasse une feuille. Maman tient sa main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SAI.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 narrateur|Quatre saisons.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Il fait chaud. Quelle saison est-ce ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Florent a nommé les quatre saisons. Un signe chacune. Maman l'a aidé.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Florent ramasse une feuille. Maman tient sa main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SAI.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les saisons de Florent</t>
+          <t>Le pot d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss veut voir une pousse dans le pot. Il verse trop d'eau. La terre déborde. Ils essuient. La pousse verte reste.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Florent marche vers l'école. Maman tient sa main. Papa a mis le manteau dans le sac. Ils passent sous un grand arbre. Il y a quatre saisons. Au printemps, Florent voit des fleurs. En été, il fait chaud. Florent boit de l'eau. En automne, les feuilles tombent. Elles sont jaunes. En hiver, Florent met son manteau. Maman dit un signe chacune. Fleurs, chaud, feuilles, manteau. Florent répète : quatre saisons. Papa arrive au portail. Quatre saisons.</t>
+          <t>Sur le rebord, un pot en terre cuite chauffe. La terre sent l'eau et le bois. Un grain de terre cuite brille. Un rai de soleil traverse la vitre. Maman ouvre un peu la fenêtre. Un oiseau chante, tout près. Tu vois le pot, Aniss ? Oui. Il y a une pousse ? Regarde bien. En ce moment, Aniss se hausse. Un fil vert sort de la terre. Il est recourbé, tout tendre. Elle est là ! Tout petit, tout vert. Je veux l'arroser. Un peu d'eau, pas trop. Papa tend le petit arrosoir. Il est bleu, un peu lourd. Aniss le penche. L'eau tombe trop vite. Glou, glou. Oh. La terre devient boue. Elle déborde sur le rebord. Un filet brun court vers le bois. Ça sent la boue, tout fort. C'est trop d'eau. On arrête. La pousse ? Elle est encore là. Le fil vert brille, tout mouillé. On essuie, Aniss. Maman tend un linge. Le linge est rêche, déjà tiède. Je frotte ? Oui. Aniss frotte le rebord. Ses doigts sont bruns, un peu. La terre tache le linge. Papa tient le pot, bien droit. C'est sale. On peut nettoyer. Le bois redevient clair, un peu. La pousse aime un peu d'eau. Pas toute la carafe. La prochaine fois, un peu. Oui. Un oiseau reprend, derrière la vitre. Le soleil chauffe le pot, encore. Elle pousse, au printemps. Oui. En été, elle sera plus grande. Pas trop d'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Florent marche vers l'école. Maman tient sa main. Papa a mis le manteau dans le sac. Ils passent sous un grand arbre. Maman dit : il y a &lt;emphasis level="moderate"&gt;quatre&lt;/emphasis&gt; saisons. Au printemps, Florent voit des fleurs. En été, il fait chaud. Florent boit de l'eau. En automne, les feuilles tombent. Elles sont jaunes. En hiver, Florent met son manteau. Maman dit un signe chacune. Fleurs, chaud, feuilles, manteau. Florent répète : quatre saisons. Papa arrive au portail. Il dit : quatre saisons.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur le rebord, un pot en terre cuite chauffe. La terre sent l'eau et le bois. Un grain de terre cuite brille. Un rai de soleil traverse la vitre. Maman ouvre un peu la fenêtre. Un oiseau chante, tout près. Tu vois le pot, Aniss ? Oui. Il y a une pousse ? Regarde bien. En ce moment, Aniss se hausse. Un fil vert sort de la terre. Il est recourbé, tout tendre. Elle est là ! Tout petit, tout vert. Je veux l'arroser. Un peu d'eau, pas trop. Papa tend le petit arrosoir. Il est bleu, un peu lourd. Aniss le penche. L'eau tombe trop vite. Glou, glou. Oh. La terre devient boue. Elle déborde sur le rebord. Un filet brun court vers le bois. Ça sent la boue, tout fort. C'est trop d'eau. On arrête. La pousse ? Elle est encore là. Le fil vert brille, tout mouillé. On essuie, Aniss. Maman tend un linge. Le linge est rêche, déjà tiède. Je frotte ? Oui. Aniss frotte le rebord. Ses doigts sont bruns, un peu. La terre tache le linge. Papa tient le pot, bien droit. C'est sale. On peut nettoyer. Le bois redevient clair, un peu. La pousse aime un peu d'eau. Pas toute la carafe. La prochaine fois, un peu. Oui. Un oiseau reprend, derrière la vitre. Le soleil chauffe le pot, encore. Elle pousse, au printemps. Oui. En été, elle sera plus grande. Pas trop d'eau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Florent marche vers l'école. Maman tient sa main. Papa a mis le manteau dans le sac. Ils passent sous un grand arbre.
-maman|Il y a quatre saisons. Au printemps, Florent voit des fleurs. En été, il fait chaud.
-narrateur|Florent boit de l'eau. En automne, les feuilles tombent. Elles sont jaunes. En hiver, Florent met son manteau. Maman dit un signe chacune. Fleurs, chaud, feuilles, manteau. Florent répète : quatre saisons. Papa arrive au portail.
-narrateur|Quatre saisons.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Sur le rebord, un pot en terre cuite chauffe.
+narrateur|La terre sent l'eau et le bois.
+narrateur|Un grain de terre cuite brille.
+narrateur|Un rai de soleil traverse la vitre.
+narrateur|Maman ouvre un peu la fenêtre.
+narrateur|Un oiseau chante, tout près.
+papa|Tu vois le pot, Aniss ?
+enfant-m|Oui.
+enfant-m|Il y a une pousse ?
+maman|Regarde bien.
+narrateur|En ce moment, Aniss se hausse.
+narrateur|Un fil vert sort de la terre.
+narrateur|Il est recourbé, tout tendre.
+enfant-m|Elle est là !
+papa|Tout petit, tout vert.
+enfant-m|Je veux l'arroser.
+maman|Un peu d'eau, pas trop.
+narrateur|Papa tend le petit arrosoir.
+narrateur|Il est bleu, un peu lourd.
+narrateur|Aniss le penche.
+narrateur|L'eau tombe trop vite.
+narrateur|Glou, glou.
+enfant-m|Oh.
+narrateur|La terre devient boue.
+narrateur|Elle déborde sur le rebord.
+narrateur|Un filet brun court vers le bois.
+narrateur|Ça sent la boue, tout fort.
+maman|C'est trop d'eau.
+papa|On arrête.
+enfant-m|La pousse ?
+maman|Elle est encore là.
+narrateur|Le fil vert brille, tout mouillé.
+papa|On essuie, Aniss.
+narrateur|Maman tend un linge.
+narrateur|Le linge est rêche, déjà tiède.
+enfant-m|Je frotte ?
+maman|Oui.
+narrateur|Aniss frotte le rebord.
+narrateur|Ses doigts sont bruns, un peu.
+narrateur|La terre tache le linge.
+narrateur|Papa tient le pot, bien droit.
+enfant-m|C'est sale.
+papa|On peut nettoyer.
+narrateur|Le bois redevient clair, un peu.
+maman|La pousse aime un peu d'eau.
+maman|Pas toute la carafe.
+enfant-m|La prochaine fois, un peu.
+papa|Oui.
+narrateur|Un oiseau reprend, derrière la vitre.
+narrateur|Le soleil chauffe le pot, encore.
+enfant-m|Elle pousse, au printemps.
+maman|Oui.
+papa|En été, elle sera plus grande.
+enfant-m|Pas trop d'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,12 +1404,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Il fait chaud. Quelle saison est-ce ?</t>
+          <t>La pousse est verte, dans le pot. Quelle saison est-ce ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Il fait chaud. Quelle saison est-ce ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pousse est verte, dans le pot. Quelle saison est-ce ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1358,12 +1419,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>été</t>
+          <t>printemps</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>été | l'été | en été</t>
+          <t>printemps | le printemps | au printemps | pousse | vert</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1378,7 +1439,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>En été, il fait chaud. Quelle saison ?</t>
+          <t>La pousse est verte. Quelle saison ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1427,7 +1488,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1499,10 +1560,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Il fait chaud. Quelle saison est-ce ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La pousse est verte, dans le pot.
+narrateur|Quelle saison est-ce ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1527,12 +1588,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Florent a nommé les quatre saisons. Un signe chacune. Maman l'a aidé.</t>
+          <t>Aniss pose l'arrosoir, bien droit. Une goutte tombe encore, puis plus. Elle est sauve. Oui. Tu as essuyé le rebord. Merci, Aniss. Le fil vert se redresse un peu. La terre est sombre, plus calme. Je la regarde. On la regarde ensemble. Une goutte sèche sur la terre cuite.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Florent a nommé les &lt;emphasis level="moderate"&gt;quatre&lt;/emphasis&gt; saisons. Un signe chacune. Maman l'a aidé.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss pose l'arrosoir, bien droit. Une goutte tombe encore, puis plus. Elle est sauve. Oui. Tu as essuyé le rebord. Merci, Aniss. Le fil vert se redresse un peu. La terre est sombre, plus calme. Je la regarde. On la regarde ensemble. Une goutte sèche sur la terre cuite.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1588,14 +1649,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1671,10 +1732,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Florent a nommé les quatre saisons. Un signe chacune. Maman l'a aidé.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss pose l'arrosoir, bien droit.
+narrateur|Une goutte tombe encore, puis plus.
+enfant-m|Elle est sauve.
+maman|Oui.
+maman|Tu as essuyé le rebord.
+papa|Merci, Aniss.
+narrateur|Le fil vert se redresse un peu.
+narrateur|La terre est sombre, plus calme.
+enfant-m|Je la regarde.
+papa|On la regarde ensemble.
+narrateur|Une goutte sèche sur la terre cuite.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1699,12 +1769,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Florent ramasse une feuille. Maman tient sa main.</t>
+          <t>Maman referme un peu la fenêtre. Le linge taché reste sur le bord. On le rince, après. Le pot est lourd, maintenant. Il a trop bu, un moment. Aniss pose un doigt près de la pousse. Il ne touche pas, il regarde.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Florent ramasse &lt;emphasis level="moderate"&gt;un&lt;/emphasis&gt;e feuille. Maman tient sa main.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman referme un peu la fenêtre. Le linge taché reste sur le bord. On le rince, après. Le pot est lourd, maintenant. Il a trop bu, un moment. Aniss pose un doigt près de la pousse. Il ne touche pas, il regarde.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1760,14 +1830,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1839,10 +1909,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Florent ramasse une feuille. Maman tient sa main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman referme un peu la fenêtre.
+narrateur|Le linge taché reste sur le bord.
+papa|On le rince, après.
+enfant-m|Le pot est lourd, maintenant.
+maman|Il a trop bu, un moment.
+narrateur|Aniss pose un doigt près de la pousse.
+narrateur|Il ne touche pas, il regarde.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,12 +1942,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le rai de soleil a bougé. Il touche encore le pot chaud. Pousse, petit. Oui. Tout doucement. La terre sent encore l'eau, tout près. Aniss reste, le nez contre la vitre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rai de soleil a bougé. Il touche encore le pot chaud. Pousse, petit. Oui. Tout doucement. La terre sent encore l'eau, tout près. Aniss reste, le nez contre la vitre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1928,14 +2003,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2007,10 +2082,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le rai de soleil a bougé.
+narrateur|Il touche encore le pot chaud.
+enfant-m|Pousse, petit.
+papa|Oui.
+maman|Tout doucement.
+narrateur|La terre sent encore l'eau, tout près.
+narrateur|Aniss reste, le nez contre la vitre.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2029,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2147,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SAI.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chemin vers l'école</t>
+          <t>rebord de fenêtre, pot en terre cuite</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Florent, maman, papa</t>
+          <t>Aniss, maman, papa</t>
         </is>
       </c>
     </row>
